--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104711_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104711_W29.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4489</v>
+        <v>5.4426</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6149</v>
+        <v>4.1837</v>
       </c>
       <c r="F2" t="n">
-        <v>0.834</v>
+        <v>1.259</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7743</v>
+        <v>4.7667</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6373</v>
+        <v>2.6288</v>
       </c>
       <c r="I2" t="n">
-        <v>2.137</v>
+        <v>2.1378</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9336</v>
+        <v>3.9158</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2992</v>
+        <v>2.285</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6344</v>
+        <v>1.6308</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8407</v>
+        <v>0.8509</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3381</v>
+        <v>0.3438</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5026</v>
+        <v>0.5071</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3701</v>
+        <v>-0.3728</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.2769</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5057</v>
+        <v>-0.0959</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.405</v>
+        <v>4.1663</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5702</v>
+        <v>0.5026</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1652</v>
+        <v>3.6638</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3437</v>
+        <v>3.7398</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1406</v>
+        <v>-0.2329</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7969000000000001</v>
+        <v>3.9727</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9091</v>
+        <v>1.3982</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2008</v>
+        <v>-1.4242</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7083</v>
+        <v>2.8223</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5654</v>
+        <v>2.3416</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0601</v>
+        <v>1.1912</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5052</v>
+        <v>1.1504</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1359</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1359</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6746</v>
+        <v>0.1094</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4104</v>
+        <v>-0.3022</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2642</v>
+        <v>0.4116</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2507</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2507</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8664</v>
+        <v>4.0643</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2785</v>
+        <v>4.4371</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5879</v>
+        <v>-0.3728</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7399</v>
+        <v>1.341</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2352</v>
+        <v>2.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9751</v>
+        <v>-0.7936</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4051</v>
+        <v>2.8998</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.4223</v>
+        <v>2.1923</v>
       </c>
       <c r="L4" t="n">
-        <v>2.8274</v>
+        <v>0.7075</v>
       </c>
       <c r="M4" t="n">
-        <v>2.3348</v>
+        <v>-1.5588</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1871</v>
+        <v>-0.0578</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1477</v>
+        <v>-1.5011</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2272</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9087</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.192</v>
+        <v>0.3379</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5363</v>
+        <v>0.29</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3443</v>
+        <v>0.0479</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5456</v>
+        <v>1.2472</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5456</v>
+        <v>1.2472</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7872</v>
+        <v>2.5892</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0306</v>
+        <v>2.9459</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8178</v>
+        <v>-0.3566</v>
       </c>
       <c r="G5" t="n">
-        <v>4.093</v>
+        <v>-1.9447</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0219</v>
+        <v>-2.484</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0711</v>
+        <v>0.5393</v>
       </c>
       <c r="J5" t="n">
-        <v>1.13</v>
+        <v>-0.5426</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2105</v>
+        <v>-2.2105</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0806</v>
+        <v>1.668</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9631</v>
+        <v>-1.4022</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8114</v>
+        <v>-0.2734</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1517</v>
+        <v>-1.1287</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7171999999999999</v>
+        <v>-0.1881</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2522</v>
+        <v>-0.0955</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9694</v>
+        <v>-0.0926</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.0231</v>
+        <v>3.584</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7724</v>
+        <v>3.584</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7152</v>
+        <v>1.8952</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0845</v>
+        <v>-1.2879</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3693</v>
+        <v>3.1831</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9439</v>
+        <v>4.0891</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.4832</v>
+        <v>2.0167</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5392</v>
+        <v>2.0723</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5335</v>
+        <v>1.117</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.2051</v>
+        <v>1.1991</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6717</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4104</v>
+        <v>2.9721</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.278</v>
+        <v>0.8176</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1324</v>
+        <v>2.1545</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1359</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0694</v>
+        <v>-0.1727</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0254</v>
+        <v>-0.4928</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0948</v>
+        <v>0.3201</v>
       </c>
       <c r="V6" t="n">
-        <v>3.5926</v>
+        <v>-2.0212</v>
       </c>
       <c r="W6" t="n">
-        <v>3.5926</v>
+        <v>-0.7739</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8328</v>
+        <v>1.8608</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1598</v>
+        <v>0.5774</v>
       </c>
       <c r="F7" t="n">
-        <v>1.673</v>
+        <v>1.2834</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5851</v>
+        <v>1.8987</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.0112</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5159</v>
+        <v>1.8875</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6941000000000001</v>
+        <v>1.8506</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0916</v>
+        <v>-0.376</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6025</v>
+        <v>2.2265</v>
       </c>
       <c r="M7" t="n">
-        <v>0.109</v>
+        <v>0.0481</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0225</v>
+        <v>0.3871</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0866</v>
+        <v>-0.3391</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3631</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3631</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2141</v>
+        <v>-0.1775</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6945</v>
+        <v>-0.135</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5197000000000001</v>
+        <v>-0.0425</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1594</v>
+        <v>-0.3155</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>M. ALLEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.706</v>
+        <v>1.1357</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2367</v>
+        <v>1.332</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.1964</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5434</v>
+        <v>0.3517</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4711</v>
+        <v>-0.1696</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0145</v>
+        <v>0.5213</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9198</v>
+        <v>1.2833</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6965</v>
+        <v>0.0172</v>
       </c>
       <c r="L8" t="n">
-        <v>3.6163</v>
+        <v>1.2661</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3765</v>
+        <v>-0.9315</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2254</v>
+        <v>-0.1868</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6018</v>
+        <v>-0.7447</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9087</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4576</v>
+        <v>0.101</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8837</v>
+        <v>0.0487</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4261</v>
+        <v>0.0523</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3421</v>
+        <v>1.0999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0457</v>
+        <v>1.4608</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2964</v>
+        <v>-0.3609</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8964</v>
+        <v>2.5426</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.471</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8874</v>
+        <v>3.0136</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8567</v>
+        <v>2.9118</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3742</v>
+        <v>-0.7002</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2309</v>
+        <v>3.612</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0396</v>
+        <v>-0.3692</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3831</v>
+        <v>0.2292</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3435</v>
+        <v>-0.5984</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4544</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5903</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6899</v>
+        <v>-0.1451</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6751</v>
+        <v>0.1228</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0148</v>
+        <v>-0.268</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3188</v>
+        <v>-0.387</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3188</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ALLEN</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9149</v>
+        <v>0.7556</v>
       </c>
       <c r="E10" t="n">
-        <v>1.146</v>
+        <v>-0.5616</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2311</v>
+        <v>1.3172</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3514</v>
+        <v>-0.5826</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1706</v>
+        <v>-0.0689</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5219</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2848</v>
+        <v>-0.7004</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0173</v>
+        <v>-0.0969</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2676</v>
+        <v>-0.6035</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9335</v>
+        <v>0.1178</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1878</v>
+        <v>0.028</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7456</v>
+        <v>0.0898</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6816</v>
+        <v>1.3658</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6816</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.118</v>
+        <v>0.1301</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1388</v>
+        <v>-0.019</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0208</v>
+        <v>0.1492</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. TORRES</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3537</v>
+        <v>0.3918</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0173</v>
+        <v>-0.214</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3364</v>
+        <v>0.6057</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3328</v>
+        <v>-0.8442</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1751</v>
+        <v>-1.3808</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1578</v>
+        <v>0.5367</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0173</v>
+        <v>-0.2332</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0173</v>
+        <v>-1.3799</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.1467</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3156</v>
+        <v>-0.6109</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1578</v>
+        <v>-0.0009</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1578</v>
+        <v>-0.61</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0208</v>
+        <v>-1.1997</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-0.5255</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0208</v>
+        <v>-0.6742</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>A. TORRES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5389</v>
+        <v>0.3854</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.529</v>
+        <v>0.0172</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9901</v>
+        <v>0.3681</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0988</v>
+        <v>0.3331</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6401</v>
+        <v>0.1752</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4587</v>
+        <v>0.1579</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4713</v>
+        <v>0.0172</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4148</v>
+        <v>0.0172</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0566</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.3159</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2254</v>
+        <v>0.1579</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4021</v>
+        <v>0.1579</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4544</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8175</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0921</v>
+        <v>0.0523</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2716</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3637</v>
+        <v>0.0523</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7328</v>
+        <v>-0.3355</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.974</v>
+        <v>-1.5908</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2412</v>
+        <v>1.2553</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8431999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3772</v>
+        <v>0.6429</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5339</v>
+        <v>0.4571</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2199</v>
+        <v>0.4652</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3696</v>
+        <v>0.4137</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1497</v>
+        <v>0.0515</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6234</v>
+        <v>0.6349</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0076</v>
+        <v>0.2292</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6158</v>
+        <v>0.4057</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0447</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0447</v>
+        <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3205</v>
+        <v>0.1092</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2998</v>
+        <v>0.2203</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0207</v>
+        <v>-0.1111</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3862</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5456</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1594</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>23.1005</v>
+        <v>23.4513</v>
       </c>
       <c r="E14" t="n">
-        <v>11.62</v>
+        <v>11.8024</v>
       </c>
       <c r="F14" t="n">
-        <v>11.4805</v>
+        <v>11.6489</v>
       </c>
       <c r="G14" t="n">
-        <v>16.8015</v>
+        <v>16.7912</v>
       </c>
       <c r="H14" t="n">
-        <v>2.817600000000001</v>
+        <v>2.8022</v>
       </c>
       <c r="I14" t="n">
-        <v>13.9838</v>
+        <v>13.989</v>
       </c>
       <c r="J14" t="n">
-        <v>14.4802</v>
+        <v>14.3827</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0005999999999999339</v>
+        <v>-0.06319999999999987</v>
       </c>
       <c r="L14" t="n">
-        <v>14.4798</v>
+        <v>14.4458</v>
       </c>
       <c r="M14" t="n">
-        <v>2.321099999999999</v>
+        <v>2.4087</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8173</v>
+        <v>2.8651</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4958000000000004</v>
+        <v>-0.4566000000000002</v>
       </c>
       <c r="P14" t="n">
-        <v>6.8156</v>
+        <v>6.8291</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.951499999999999</v>
+        <v>-7.9672</v>
       </c>
       <c r="R14" t="n">
-        <v>14.767</v>
+        <v>14.7962</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7677</v>
+        <v>-1.416</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.481</v>
+        <v>-1.1651</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2866000000000001</v>
+        <v>-0.2509</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="W14" t="n">
-        <v>6.572100000000001</v>
+        <v>6.5517</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.3216</v>
+        <v>-5.3045</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1909</v>
+        <v>3.3067</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8395</v>
+        <v>3.9966</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6486</v>
+        <v>-0.6899</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8864</v>
+        <v>0.8912</v>
       </c>
       <c r="H15" t="n">
-        <v>2.369</v>
+        <v>2.3717</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4826</v>
+        <v>-1.4805</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6986</v>
+        <v>1.6918</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2638</v>
+        <v>2.258</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5652</v>
+        <v>-0.5662</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8123</v>
+        <v>-0.8006</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1051</v>
+        <v>0.1137</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9174</v>
+        <v>-0.9143</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1451</v>
+        <v>1.2577</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3446</v>
+        <v>0.5128</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8005</v>
+        <v>0.7449</v>
       </c>
       <c r="V15" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7963</v>
+        <v>1.792</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1322</v>
+        <v>1.8096</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4134</v>
+        <v>2.4508</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2811</v>
+        <v>-0.6412</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5322</v>
+        <v>2.5301</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8317</v>
+        <v>-0.8302</v>
       </c>
       <c r="I16" t="n">
-        <v>3.364</v>
+        <v>3.3603</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2121</v>
+        <v>3.202</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6965</v>
+        <v>-0.7002</v>
       </c>
       <c r="L16" t="n">
-        <v>3.9085</v>
+        <v>3.9022</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1353</v>
+        <v>-0.13</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5446</v>
+        <v>-0.5419</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0819</v>
+        <v>-0.4019</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8143</v>
+        <v>-0.135</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8962</v>
+        <v>-0.2669</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.613</v>
+        <v>-0.6162</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0557</v>
+        <v>0.4415</v>
       </c>
       <c r="E17" t="n">
-        <v>0.624</v>
+        <v>0.7395</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6797</v>
+        <v>-0.2979</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5148</v>
+        <v>0.5159</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5921</v>
+        <v>0.5916</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0772</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7929</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3174</v>
+        <v>-0.3143</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2029</v>
+        <v>-0.2012</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1145</v>
+        <v>-0.113</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7977</v>
+        <v>-0.302</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2082</v>
+        <v>-0.0907</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5895</v>
+        <v>-0.2113</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.178</v>
+        <v>-0.771</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9974</v>
+        <v>-0.1936</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8194</v>
+        <v>-0.5775</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7996</v>
+        <v>0.6353</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5679999999999999</v>
+        <v>0.6802</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2316</v>
+        <v>-0.0449</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9834000000000001</v>
+        <v>1.7649</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1158</v>
+        <v>0.3652</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.0991</v>
+        <v>1.3997</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8162</v>
+        <v>-1.1296</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6838</v>
+        <v>0.3149</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1324</v>
+        <v>-1.4446</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2272</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5903</v>
+        <v>-2.7316</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3631</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6893</v>
+        <v>0.0278</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4169</v>
+        <v>-0.3163</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2725</v>
+        <v>0.3441</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1594</v>
+        <v>0.387</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1594</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6041</v>
+        <v>-1.3985</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8835</v>
+        <v>-1.8973</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7206</v>
+        <v>0.4988</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6337</v>
+        <v>-2.7976</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6768999999999999</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0433</v>
+        <v>-2.2316</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7736</v>
+        <v>-0.9929</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3689</v>
+        <v>0.1099</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4047</v>
+        <v>-1.1029</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.14</v>
+        <v>-1.8047</v>
       </c>
       <c r="N19" t="n">
-        <v>0.308</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.448</v>
+        <v>-1.1287</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8175</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7262</v>
+        <v>-1.5934</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9087</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8065</v>
+        <v>1.469</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0221</v>
+        <v>0.5313</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2156</v>
+        <v>0.9377</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3862</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0913</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8402</v>
+        <v>-1.87</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6151</v>
+        <v>-0.619</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2252</v>
+        <v>-1.251</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2767</v>
+        <v>-1.2743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8084</v>
+        <v>0.8097</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0851</v>
+        <v>-2.084</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1986</v>
+        <v>-0.2008</v>
       </c>
       <c r="K20" t="n">
-        <v>0.553</v>
+        <v>0.5516</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7516</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.078</v>
+        <v>-1.0734</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2554</v>
+        <v>0.2581</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3335</v>
+        <v>-1.3315</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3364</v>
+        <v>-0.3681</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1893</v>
+        <v>-0.1906</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1471</v>
+        <v>-0.1775</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>J. COBBS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1463</v>
+        <v>-2.1636</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8939</v>
+        <v>-1.4172</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2524</v>
+        <v>-0.7464</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6367</v>
+        <v>-1.8976</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3133</v>
+        <v>0.1491</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3234</v>
+        <v>-2.0467</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.831</v>
+        <v>-0.6807</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2532</v>
+        <v>0.0345</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5778</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8058</v>
+        <v>-1.2169</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0601</v>
+        <v>0.1146</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7456</v>
+        <v>-1.3315</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4905</v>
+        <v>-0.266</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1642</v>
+        <v>-0.5089</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3262</v>
+        <v>0.2429</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. COBBS</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3151</v>
+        <v>-2.5339</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5316</v>
+        <v>-2.2552</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7835</v>
+        <v>-0.2786</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9006</v>
+        <v>-2.6371</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1472</v>
+        <v>-0.3131</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0478</v>
+        <v>-2.324</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6798</v>
+        <v>-1.8346</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0346</v>
+        <v>-0.2553</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7143</v>
+        <v>-1.5793</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2208</v>
+        <v>-0.8025</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1127</v>
+        <v>-0.0578</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3335</v>
+        <v>-0.7447</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4146</v>
+        <v>0.1032</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6247</v>
+        <v>-0.193</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2101</v>
+        <v>0.2962</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.434</v>
+        <v>-2.711</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5937</v>
+        <v>-2.1376</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8403</v>
+        <v>-0.5734</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7471</v>
+        <v>-1.7468</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8686</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6157</v>
+        <v>-2.6142</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4372</v>
+        <v>-0.4461</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3577</v>
+        <v>0.3512</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.7973</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3099</v>
+        <v>-1.3007</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5109</v>
+        <v>0.5162</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8208</v>
+        <v>-1.8169</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0735</v>
+        <v>-0.3496</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9527</v>
+        <v>-0.4835</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1207</v>
+        <v>0.1339</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3804</v>
+        <v>-3.1318</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3595</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0209</v>
+        <v>-2.218</v>
       </c>
       <c r="G24" t="n">
-        <v>0.529</v>
+        <v>0.5268</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3546</v>
+        <v>0.3559</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1744</v>
+        <v>0.1708</v>
       </c>
       <c r="J24" t="n">
-        <v>1.6418</v>
+        <v>1.6288</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3923</v>
+        <v>0.3857</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2496</v>
+        <v>1.243</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1128</v>
+        <v>-1.102</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0376</v>
+        <v>-0.0298</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0752</v>
+        <v>-1.0722</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.635</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7288</v>
+        <v>0.5283</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0944</v>
+        <v>0.3758</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6344</v>
+        <v>0.1524</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W24" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6349</v>
+        <v>-3.6456</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3158</v>
+        <v>-2.5034</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3191</v>
+        <v>-1.1421</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.8472</v>
+        <v>-2.8458</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4126</v>
+        <v>-1.4078</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4347</v>
+        <v>-1.438</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0189</v>
+        <v>-1.028</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.405</v>
+        <v>-1.4069</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3861</v>
+        <v>0.3789</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8284</v>
+        <v>-1.8179</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0076</v>
+        <v>-0.0009</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.8208</v>
+        <v>-1.8169</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8551</v>
+        <v>0.1288</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9338</v>
+        <v>-0.1097</v>
       </c>
       <c r="U25" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.2385</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.4782</v>
+        <v>-0.4733</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.4782</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.8347</v>
+        <v>-8.8559</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.1668</v>
+        <v>-6.8987</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6678</v>
+        <v>-1.9572</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.6897</v>
+        <v>-8.6912</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.5088</v>
+        <v>-5.5107</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.1809</v>
+        <v>-3.1805</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.3308</v>
+        <v>-6.343</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.3435</v>
+        <v>-5.3519</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.9873</v>
+        <v>-0.9912</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.359</v>
+        <v>-2.3481</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1654</v>
+        <v>-0.1588</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.1936</v>
+        <v>-2.1893</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S26" t="n">
-        <v>2.537</v>
+        <v>1.5166</v>
       </c>
       <c r="T26" t="n">
-        <v>1.5718</v>
+        <v>0.8589</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
       <c r="W26" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.4101</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-23.1003</v>
+        <v>-21.5235</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.4804</v>
+        <v>-11.6489</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.6198</v>
+        <v>-9.8744</v>
       </c>
       <c r="G27" t="n">
-        <v>-16.8015</v>
+        <v>-16.7911</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.817600000000001</v>
+        <v>-2.8022</v>
       </c>
       <c r="I27" t="n">
-        <v>-13.9839</v>
+        <v>-13.9891</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.321399999999999</v>
+        <v>-2.4085</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.8172</v>
+        <v>-2.8653</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4960000000000003</v>
+        <v>0.4565</v>
       </c>
       <c r="M27" t="n">
-        <v>-14.4805</v>
+        <v>-14.3826</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.0005999999999999062</v>
+        <v>0.06310000000000004</v>
       </c>
       <c r="O27" t="n">
-        <v>-14.4799</v>
+        <v>-14.4455</v>
       </c>
       <c r="P27" t="n">
-        <v>-6.815599999999999</v>
+        <v>-6.8289</v>
       </c>
       <c r="Q27" t="n">
-        <v>-14.7671</v>
+        <v>-14.7959</v>
       </c>
       <c r="R27" t="n">
-        <v>7.9514</v>
+        <v>7.9671</v>
       </c>
       <c r="S27" t="n">
-        <v>1.767399999999999</v>
+        <v>3.3438</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2866000000000002</v>
+        <v>0.2511000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4809</v>
+        <v>3.0927</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.2506</v>
+        <v>-1.2471</v>
       </c>
       <c r="W27" t="n">
-        <v>5.3216</v>
+        <v>5.3046</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.5721</v>
+        <v>-6.551699999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104711_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104711_W29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-5.3045</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104711_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.551699999999999</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
